--- a/Planificación/planifSignBridge.xlsx
+++ b/Planificación/planifSignBridge.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/aleixbenet/Desktop/UNIVERSITAT/3r/2n Semestre/Laboratori Integrat del Software/SignBridge/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40633E6C-9A33-C545-B4A7-B523769F5165}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{3FB0342E-9700-554B-88CA-27F53F7EF9DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="760" yWindow="500" windowWidth="28040" windowHeight="16340" xr2:uid="{00DAC7DF-7952-1748-91A6-61FAC0B48BE2}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" xr2:uid="{00DAC7DF-7952-1748-91A6-61FAC0B48BE2}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="34">
   <si>
     <t>SEMANA</t>
   </si>
@@ -104,28 +104,40 @@
     <t>junio</t>
   </si>
   <si>
-    <t>Definir alcance del proyecto (lengua, palabras sueltas…, numero de signos...)</t>
-  </si>
-  <si>
-    <t>Definir setup (Mediapipe de Google?, openCV, python, java, flutter….)</t>
-  </si>
-  <si>
-    <t>Posibles necesidades (webcam, fondo blanco, centrado…)</t>
-  </si>
-  <si>
-    <t>Creación del dataset + inicio diseño algoritmo clasificador</t>
-  </si>
-  <si>
-    <t>Instal·lación setup + decisiones de diseño (último de la semana)</t>
-  </si>
-  <si>
-    <t>REQUISITOS</t>
-  </si>
-  <si>
-    <t>Lista</t>
-  </si>
-  <si>
-    <t>Priorizar</t>
+    <t>EXAMENS</t>
+  </si>
+  <si>
+    <t>CREACIÓN DE LA BD, CREACIÓN  DEL DATASET, BUSCAR MEJOR ALGORITMO CLASIFICADOR,  DESARROLLAR EL SCRIPT QUE COMPARE</t>
+  </si>
+  <si>
+    <t>TERMINAR EL DESARROLLO DEL SCRIPT CLASIFICADOR I, TENER EL DATASET HECHO</t>
+  </si>
+  <si>
+    <t>CLASIFICADOR I FUNCIONA, PLANTEAMIENTO TRADUCIR PALABRAS</t>
+  </si>
+  <si>
+    <t>(pruebas, eficacia, casos)</t>
+  </si>
+  <si>
+    <t>INVESTIGAR HERRAMIENTA VC</t>
+  </si>
+  <si>
+    <t>SEMANA 16-22</t>
+  </si>
+  <si>
+    <t>3 MIEMBROS</t>
+  </si>
+  <si>
+    <t>Tema Dataset</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Clasificador </t>
+  </si>
+  <si>
+    <t>PARALELAMENTE: UI  &amp;  SEGONA PART</t>
+  </si>
+  <si>
+    <t>SEGUIR</t>
   </si>
 </sst>
 </file>
@@ -161,7 +173,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -195,6 +207,18 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="1"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -211,7 +235,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -220,21 +244,25 @@
     <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="17" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -569,15 +597,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D4B48474-F053-E24E-A774-FA0787617C53}">
-  <dimension ref="A2:K24"/>
+  <dimension ref="A2:L24"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C2" s="1" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A4" s="5" t="s">
         <v>19</v>
       </c>
@@ -585,144 +613,174 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A5" s="8" t="s">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A5" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="B5" s="12" t="s">
+      <c r="B5" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="C5" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="K5" s="1" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A6" s="8"/>
-      <c r="B6" s="12"/>
-      <c r="C6" t="s">
-        <v>23</v>
-      </c>
-      <c r="K6" t="s">
+      <c r="C5" s="7"/>
+      <c r="I5" s="2" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A7" s="8"/>
-      <c r="B7" s="12"/>
-      <c r="C7" t="s">
-        <v>26</v>
-      </c>
-      <c r="K7" t="s">
+      <c r="J5" s="16"/>
+      <c r="K5" s="2" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A8" s="8"/>
-      <c r="B8" s="12"/>
-      <c r="C8" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A9" s="8"/>
+      <c r="L5" s="16" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A6" s="11"/>
+      <c r="B6" s="10"/>
+      <c r="I6" s="16"/>
+      <c r="J6" s="16"/>
+      <c r="K6" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="L6" s="16" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A7" s="11"/>
+      <c r="B7" s="10"/>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A8" s="11"/>
+      <c r="B8" s="10"/>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A9" s="11"/>
       <c r="B9" s="2"/>
       <c r="C9" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A10" s="8"/>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A10" s="11"/>
       <c r="B10" s="2"/>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A11" s="8"/>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A11" s="11"/>
       <c r="B11" s="2" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A12" s="8"/>
+      <c r="C11" s="14" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A12" s="11"/>
       <c r="B12" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A13" s="8"/>
+      <c r="C12" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A13" s="11"/>
       <c r="B13" s="2" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A14" s="9" t="s">
+      <c r="C13" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="D13" s="15"/>
+      <c r="E13" s="15"/>
+      <c r="F13" s="15"/>
+      <c r="G13" s="15"/>
+      <c r="I13" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A14" s="12" t="s">
         <v>18</v>
       </c>
       <c r="B14" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A15" s="9"/>
+      <c r="C14" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A15" s="12"/>
       <c r="B15" s="3" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A16" s="9"/>
+      <c r="C15" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A16" s="12"/>
       <c r="B16" s="3" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A17" s="10" t="s">
+      <c r="C16" s="13"/>
+      <c r="D16" s="13"/>
+      <c r="E16" s="13"/>
+      <c r="F16" s="13"/>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A17" s="9" t="s">
         <v>20</v>
       </c>
       <c r="B17" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A18" s="10"/>
+      <c r="C17" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="D17" s="13"/>
+      <c r="E17" s="13"/>
+      <c r="F17" s="13"/>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A18" s="9"/>
       <c r="B18" s="6" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A19" s="10"/>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A19" s="9"/>
       <c r="B19" s="6" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A20" s="10"/>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A20" s="9"/>
       <c r="B20" s="6" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A21" s="10"/>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A21" s="9"/>
       <c r="B21" s="6" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A22" s="10"/>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A22" s="9"/>
       <c r="B22" s="6" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A23" s="11" t="s">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A23" s="8" t="s">
         <v>21</v>
       </c>
       <c r="B23" s="4" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A24" s="11"/>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A24" s="8"/>
       <c r="B24" s="4" t="s">
         <v>15</v>
       </c>
